--- a/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_CHEMISTRY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_CHEMISTRY\Kailash\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -93,7 +93,7 @@
     <t>Particulate Nature of Matter</t>
   </si>
   <si>
-    <t>NEET  SYLLABUS</t>
+    <t>IIT SYLLABUS</t>
   </si>
 </sst>
 </file>

--- a/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_CHEMISTRY\Kailash\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -799,9 +799,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="H8:I42 E1:K1 E3:K7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H8:I40">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K7">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
